--- a/nr-update-patient/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-medecin.xlsx
+++ b/nr-update-patient/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-medecin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:27:16+00:00</t>
+    <t>2025-10-21T13:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
